--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,34 +30,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,27 +76,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -461,10 +472,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
@@ -509,18 +525,14 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Назначение: Финализация заявки</t>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Назначение: Финализация заявки. Источник правды: BPMN ump-finalisation-ncins-pa.bpmn (PR NCINS). После create-contract — Parallel Gateway и 3× ea-send-documents.v1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -531,11 +543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,12 +564,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Согласование</t>
         </is>
@@ -584,11 +600,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,7 +615,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -620,249 +631,252 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Минимальная информация для определения необходимости проведения НТ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>[ump-finalisation-ncins-pa]: Start → get-application-data → Service Task create-contract (Job ump-prepare-finalisation-ncins-pa.create-contract, POST /v1/ins-contracts) → Connector ump-document-connectors.ea-send-documents.v1 (ЭА/AC, stopInIncident=false) → End. processType=FINALISATION (STATIC).</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Confluence + BPMN</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>[ump-finalisation-ncins-pa] (BPMN FINAL):
+1) Start → get-application-data (processType=FINALISATION STATIC)
+2) Service Task ump-finalisation-ncins-pa.create-contract (POST /v1/ins-contracts)
+3) Parallel Gateway split → 3× Connector ump-document-connectors.ea-send-documents.v1:
+   • acId=agreementLink, stopInIncident=false
+   • acId=policyLink, stopInIncident=false
+   • acId=contractLink, stopInIncident=false
+4) Parallel Gateway join → End
+MultiInstance на EA в финальном BPMN нет (было в ранних версиях).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>BPMN PR: 3 parallel ea-send</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Синхронные вызовы. По аналогии с prepare: несколько секунд на каждый sync-вызов (TBD точное число с НТ).</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Синхронные вызовы. Несколько секунд на каждый sync-вызов (TBD точное число с НТ). 3 EA идут параллельно.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>несколько секунд / вызов</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>≈85/час среднее, ≈170/час макс (заявки, дошедшие до финала от 15000/мес).</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>15000×~95%</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>≈85/час среднее, ≈170/час макс (дошедшие до финала от 15000/мес). На EA-коннектор ×3 вызова на заявку → ~255–510/час пик на connector type.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>15000×~95%; EA ×3</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>[GET /applications/{id}] ~85–170/час
-[POST /v1/ins-contracts] АБ Страхование Учет ~85–170/час
-[ump-document-connectors.ea-send-documents.v1] ЭА через AC ~85–170/час (МОК на НТ)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>2 зависимости: АБ + AC1.0/ЭА</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[get-application-data] ~85–170/час
+[ump-finalisation-ncins-pa.create-contract / POST /v1/ins-contracts] ~85–170/час
+[ump-document-connectors.ea-send-documents.v1] ×3 параллельно ≈255–510/час на тип (agreementLink / policyLink / contractLink) — МОК на НТ</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>АБ + 3× EA/AC</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -878,7 +892,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -894,288 +908,646 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2. Полная информация для проведения НТ (заполняется, только если получено заключение от инженера о необходимости проведения НТ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="140" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Инициатор процесса: {"businessKey": "550e8400-e29b-41d4-a716-446655440006"} + processType=FINALISATION (const).
-Get application request: {"businessKey": "..."}
-Create contract request (пример бэкенда): inn, email, contractNumber (НЕ статический — из /v1/ins-contracts/contract-number), dates, sums, paymentType, links, insuranceObjects, ownerId, phone, legalAddress, sellerId, sellerChannel, programId=1.
-EA: agreementLink/contractLink/policyLink из get; stopInIncident=false.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>На int нагенерить список contractNumber и отдать НТ; нужна интеграция стенда НТ</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Старт: businessKey + processType=FINALISATION (STATIC).
+Create contract request (пример): inn, email, contractNumber (НЕ статический — из /v1/ins-contracts/contract-number), dates, sums, paymentType, agreementLink/contractLink, insuranceObjects, ownerId, phone, legalAddress, sellerId, sellerChannel=SFA, programId.
+EA: 3 вызова с acId из get-application; stopInIncident=false.
+На int нагенерить список contractNumber для НТ; нужна интеграция стенда с контуром договоров.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Разные contractNumber на каждый прогон</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Get: success → данные + getProcessParams=SUCCESS; error → getProcessParams=ERROR.
-Create contract: success → result=SUCCESS, errorMessage=null; error → result=ERROR, errorMessage=лог.
-EA Response: необязателен.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Get: getProcessParams=SUCCESS|ERROR.
+Create contract: result=SUCCESS, errorMessage=null | result=ERROR + errorMessage.
+EA Response: необязателен; при отсутствии документов не обязан инцидент (stopInIncident=false).</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SUCCESS/ERROR по таскам</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>БД UMP не изменяется (нет UMP API/коннекторов на изменение сущностей UMP). Договор создаётся во внешней АБ; документы — в ЭА (на НТ мок).</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Данные в рамках работы метода в UMP DB не изменяются</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>БД UMP не изменяется. Договор — во внешней АБ; документы — в ЭА (на НТ мок).</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>UMP DB без изменений</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Мок на сохранение в ЭА (без AC реальный запрос падает). АБ ins-contracts — нужен стенд/интеграция. stopInIncident=false — не падать при отсутствующих документах.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Мок EA connector; живой/стендовый POST /v1/ins-contracts</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Мок на 3× ea-send-documents.v1. АБ ins-contracts — живой/стендовый. stopInIncident=false.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Мок EA ×3; стенд POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Sync: несколько секунд (TBD). Мок ЭА — в том же бюджете.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Sync: несколько секунд (TBD). Мок ЭА — в том же бюджете; параллельный join ждёт все 3.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>несколько сек</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1) Success: get→create contract→mock EA→SUCCESS.
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1) Success: get→create-contract→3× mock EA (parallel)→join→SUCCESS.
 2) get ERROR.
-3) create contract ERROR.
+3) create-contract ERROR.
 4) EA без документов — не обязан инцидент.
-Повторяемый прогон: разные contractNumber.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Последовательность sync-тасок + мок EA</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+Повторяемый прогон: уникальный contractNumber.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>create-contract + 3 parallel ea-send</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НТ пререквизиты :: Worker ump-finalisation-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Шаги из ump-finalisation-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>BPMN id</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Type / called process</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Ключевые параметры</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>STATIC / DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>startEvent</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>businessKey</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>service-task-get-params</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Получить данные</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>processType=FINALISATION; outs: agreementLink, policyLink, contractLink, …</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>STATIC processType; DYNAMIC businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>service-task-create-contract</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Создать договор</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ump-finalisation-ncins-pa.create-contract</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/ins-contracts; out result/errorMessage</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC payload</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Gateway_09hug5l</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Parallel split</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>parallelGateway</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>3 ветки EA</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>send-documents-to-EA1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>EA agreement</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ump-document-connectors.ea-send-documents.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>acId=agreementLink; stopInIncident=false; retries=1</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stopInIncident; DYNAMIC acId</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>send-documents-to-EA</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>EA policy</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>ump-document-connectors.ea-send-documents.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>acId=policyLink; stopInIncident=false</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stopInIncident; DYNAMIC acId</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>send-documents-to-EA2</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>EA contract</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ump-document-connectors.ea-send-documents.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>acId=contractLink; stopInIncident=false</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>STATIC stopInIncident; DYNAMIC acId</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Gateway_1sccgl0</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Parallel join</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>parallelGateway</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>ожидание 3 веток</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>endEvent</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Методы и примеры (код)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -477,7 +478,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -493,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -525,10 +526,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Назначение: Финализация заявки. Источник правды: BPMN ump-finalisation-ncins-pa.bpmn (PR NCINS). После create-contract — Parallel Gateway и 3× ea-send-documents.v1.</t>
+          <t>FinalisationWorker → POST /v1/ins-contracts + 3× ea-send-documents.v1 (внешний connector).</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -564,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -631,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -674,203 +675,198 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>[ump-finalisation-ncins-pa] (BPMN FINAL):
-1) Start → get-application-data (processType=FINALISATION STATIC)
-2) Service Task ump-finalisation-ncins-pa.create-contract (POST /v1/ins-contracts)
-3) Parallel Gateway split → 3× Connector ump-document-connectors.ea-send-documents.v1:
-   • acId=agreementLink, stopInIncident=false
-   • acId=policyLink, stopInIncident=false
-   • acId=contractLink, stopInIncident=false
-4) Parallel Gateway join → End
-MultiInstance на EA в финальном BPMN нет (было в ранних версиях).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>BPMN PR: 3 parallel ea-send</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1) get-application-data (FINALISATION)
+2) ump-finalisation-ncins-pa.create-contract → FinalisationWorker → NibNcinsAccClient POST /v1/ins-contracts
+3) Parallel Gateway → 3× ump-document-connectors.ea-send-documents.v1 (acId=agreementLink|policyLink|contractLink, stopInIncident=false)
+4) Join → End</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>FinalisationWorker + NibNcinsAccClient</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Синхронные вызовы. Несколько секунд на каждый sync-вызов (TBD точное число с НТ). 3 EA идут параллельно.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>несколько секунд / вызов</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Sync get + create-contract (+retries). 3 EA параллельно. Несколько секунд/вызов (TBD).</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>несколько сек</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>≈85/час среднее, ≈170/час макс (дошедшие до финала от 15000/мес). На EA-коннектор ×3 вызова на заявку → ~255–510/час пик на connector type.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>15000×~95%; EA ×3</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>≈85/170 заявок; EA ×3 → ~255–510 вызовов connector/час в пике.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>×3 EA</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>[get-application-data] ~85–170/час
-[ump-finalisation-ncins-pa.create-contract / POST /v1/ins-contracts] ~85–170/час
-[ump-document-connectors.ea-send-documents.v1] ×3 параллельно ≈255–510/час на тип (agreementLink / policyLink / contractLink) — МОК на НТ</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>АБ + 3× EA/AC</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>[GET applications] ~85–170
+[POST /v1/ins-contracts] ~85–170
+[ea-send-documents.v1 ×3] ~255–510</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>integration.nib.corp-ncins-acc-api.url</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -892,7 +888,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -908,7 +904,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -951,234 +947,236 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Старт: businessKey + processType=FINALISATION (STATIC).
-Create contract request (пример): inn, email, contractNumber (НЕ статический — из /v1/ins-contracts/contract-number), dates, sums, paymentType, agreementLink/contractLink, insuranceObjects, ownerId, phone, legalAddress, sellerId, sellerChannel=SFA, programId.
-EA: 3 вызова с acId из get-application; stopInIncident=false.
-На int нагенерить список contractNumber для НТ; нужна интеграция стенда с контуром договоров.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Разные contractNumber на каждый прогон</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>HTTP: POST {nib.url}/v1/ins-contracts
+Headers (IT): A-userId=AAAX22, A-customerId=AAAX22, A-clientType=BACKEND, A-channelId=ump (+ optional A-userIp, A-projectId=ncins)
+Camunda/ContractCreateInputVariables (из FinalisationWorkerIT.createValidVariables):
+programId=3, inn=7707083893, email=romashka@rambler.ru, contractNumber=Z6922/888/ABR14880/10, dates, sums, debitAccount, duration=12, paymentType=payment_account, contract/policy/agreementLink, insuranceObjects[], ownerId=AAAX22, phoneNumber, legalAddress, sellerId, sellerChannel=SFA
+URL: http://corp-gateway-test.../corp-ncins-acc-api (yaml)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>FinalisationWorkerIT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Get: getProcessParams=SUCCESS|ERROR.
-Create contract: result=SUCCESS, errorMessage=null | result=ERROR + errorMessage.
-EA Response: необязателен; при отсутствии документов не обязан инцидент (stopInIncident=false).</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SUCCESS/ERROR по таскам</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 201 {} (void).
+Worker out success: {"result":"SUCCESS","errorMessage":null}
+5xx: 3 retry → {"result":"ERROR","errorMessage":"..."}
+401: refresh token + retry (IT).
+EA response необязателен; stopInIncident=false.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>201 + result=SUCCESS</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>БД UMP не изменяется. Договор — во внешней АБ; документы — в ЭА (на НТ мок).</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>UMP DB без изменений</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>UMP DB не меняется. Договор создаётся во внешней АБ (NIB). Документы — ЭА через connector.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>внешняя АБ + ЭА</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Мок на 3× ea-send-documents.v1. АБ ins-contracts — живой/стендовый. stopInIncident=false.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Мок EA ×3; стенд POST /v1/ins-contracts</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>NIB — стенд/WireMock (как IT). 3× ea-send — мок connector на НТ. Нужны уникальные contractNumber.</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>WireMock POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Sync: несколько секунд (TBD). Мок ЭА — в том же бюджете; параллельный join ждёт все 3.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Несколько секунд; join ждёт 3 EA.</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>несколько сек</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1) Success: get→create-contract→3× mock EA (parallel)→join→SUCCESS.
-2) get ERROR.
-3) create-contract ERROR.
-4) EA без документов — не обязан инцидент.
-Повторяемый прогон: уникальный contractNumber.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>create-contract + 3 parallel ea-send</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1) Success get→create→3 EA.
+2) create 503 → ERROR after 3 retries.
+3) 401 token refresh.
+4) EA без docs — не обязан инцидент.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>FinalisationWorkerIT</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -1195,15 +1193,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1216,14 +1214,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Шаги из ump-finalisation-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+          <t>Методы finalisation (develop + IT)</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1233,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN id</t>
+          <t>BPMN / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1245,305 +1243,113 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / called process</t>
+          <t>Type / HTTP</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ключевые параметры</t>
+          <t>Request / Input</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>STATIC / DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Response / Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>startEvent</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>businessKey</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>processType=FINALISATION</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>поля договора + agreement/policy/contractLink</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>service-task-get-params</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Получить данные</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>processType=FINALISATION; outs: agreementLink, policyLink, contractLink, …</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>STATIC processType; DYNAMIC businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ump-finalisation-ncins-pa.create-contract</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>FinalisationWorker</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ContractRequestDto + headers A-*</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>201 {}; worker result=SUCCESS|ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>service-task-create-contract</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Создать договор</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ump-finalisation-ncins-pa.create-contract</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>POST /v1/ins-contracts; out result/errorMessage</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC payload</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Gateway_09hug5l</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Parallel split</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>parallelGateway</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>3 ветки EA</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>send-documents-to-EA1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>EA agreement</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ea-send ×3</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>внешний connector</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>ump-document-connectors.ea-send-documents.v1</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>acId=agreementLink; stopInIncident=false; retries=1</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stopInIncident; DYNAMIC acId</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>send-documents-to-EA</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>EA policy</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>ump-document-connectors.ea-send-documents.v1</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>acId=policyLink; stopInIncident=false</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stopInIncident; DYNAMIC acId</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>send-documents-to-EA2</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>EA contract</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ump-document-connectors.ea-send-documents.v1</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>acId=contractLink; stopInIncident=false</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>STATIC stopInIncident; DYNAMIC acId</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Gateway_1sccgl0</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Parallel join</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>parallelGateway</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>ожидание 3 веток</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>endEvent</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>acId=agreement|policy|contractLink; stopInIncident=false</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>вне репы</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="220" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -960,21 +960,76 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>HTTP: POST {nib.url}/v1/ins-contracts
-Headers (IT): A-userId=AAAX22, A-customerId=AAAX22, A-clientType=BACKEND, A-channelId=ump (+ optional A-userIp, A-projectId=ncins)
-Camunda/ContractCreateInputVariables (из FinalisationWorkerIT.createValidVariables):
-programId=3, inn=7707083893, email=romashka@rambler.ru, contractNumber=Z6922/888/ABR14880/10, dates, sums, debitAccount, duration=12, paymentType=payment_account, contract/policy/agreementLink, insuranceObjects[], ownerId=AAAX22, phoneNumber, legalAddress, sellerId, sellerChannel=SFA
-URL: http://corp-gateway-test.../corp-ncins-acc-api (yaml)</t>
+          <t xml:space="preserve">У воркера отсутствует HTTP-эндпоинт.
+Вызов происходит напрямую в Camunda.
+Camunda на базе Java скрипта, инструкция — https://confluence.moscow.alfaintra.net/pages/viewpage.action?pageId=2136656813
+Пример запроса:
+Map&lt;String, Object&gt; variables = Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003", // id заявки (UMP application)
+  "productCode", "NON_CREDIT_INSURANCE" // const
+);
+final ProcessInstanceEvent processInstanceEvent = client
+  .newCreateInstanceCommand()
+  .bpmnProcessId("ump-finalisation-ncins-pa")
+  .latestVersion()
+  .variables(variables)
+  .send()
+  .join();
+Параметры для запроса:
+1. businessKey — UUID заявки (параметризовать на объём ≥ ЧПН)
+2. productCode — const NON_CREDIT_INSURANCE (параметризация не нужна)
+--- Шаги (FinalisationWorkerIT) ---
+1) get-application-data processType=FINALISATION
+Map.of("businessKey", "550e8400-e29b-41d4-a716-446655110000", "processType", "FINALISATION");
+HTTP: GET .../applications/550e8400-e29b-41d4-a716-446655110000?include=PARTICIPANT&amp;include=PRODUCT
+2) create-contract type=ump-finalisation-ncins-pa.create-contract
+Camunda vars (createValidVariables из IT) — эквивалент Map:
+Map.of(
+  "programId", 3,
+  "inn", "7707083893",
+  "email", "romashka@rambler.ru",
+  "contractNumber", "Z6922/888/ABR14880/10", // параметризовать на каждый прогон
+  "beginDate", "2027-07-01T00:00:00Z",
+  "endDate", "2028-07-01T00:00:00Z",
+  "insuranceSum", 150000.93,
+  "insurancePremium", 50000.55,
+  "signDate", "2027-07-01T00:00:00Z",
+  "debitAccount", "40802810000000000000",
+  "duration", 12,
+  "paymentType", "payment_account",
+  "contractLink", "http://contract.link",
+  "policyLink", "http://policy.link",
+  "agreementLink", "http://agreement.link",
+  "ownerId", "AAAX22",
+  "phoneNumber", "+79001234567",
+  "legalAddress", "г. Пушкино ул. Колотушкина д. 14/88",
+  "sellerId", "ASASAS",
+  "sellerChannel", "SFA"
+  // + insuranceObjects[] (2 объекта, см. FinalisationWorkerIT)
+);
+HTTP:
+POST {integration.nib.corp-ncins-acc-api.url}/v1/ins-contracts
+Headers:
+  A-userId: AAAX22
+  A-customerId: AAAX22
+  A-clientType: BACKEND
+  A-channelId: ump
+Body: ContractRequestDto (из маппера ContractCreateInputVariables)
+3) 3× connector ea-send-documents.v1 (вне репы)
+acId = agreementLink | policyLink | contractLink; stopInIncident=false
+</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>FinalisationWorkerIT</t>
+          <t>Map.of start + POST /v1/ins-contracts (IT)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
+          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.
+Параметризовать businessKey (≥ ЧПН). productCode — const NON_CREDIT_INSURANCE.
+Источник примеров: develop ump-ncins-pa *WorkerIT + stubs.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -983,7 +1038,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="180" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -996,21 +1051,26 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>HTTP 201 {} (void).
-Worker out success: {"result":"SUCCESS","errorMessage":null}
-5xx: 3 retry → {"result":"ERROR","errorMessage":"..."}
-401: refresh token + retry (IT).
-EA response необязателен; stopInIncident=false.</t>
+          <t>HTTP create-contract: 201 Created, body {{}}
+Camunda worker out success:
+{ "result": "SUCCESS", "errorMessage": null }
+HTTP 503 → 3 retry →:
+{ "result": "ERROR", "errorMessage": "&lt;log&gt;" }
+HTTP 401 → refresh token + retry (IT shouldRetryWithNewTokenOn401)
+get-application-data: getProcessParams = SUCCESS | ERROR
+EA connector: response необязателен; при отсутствии документов не обязан инцидент.</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>201 + result=SUCCESS</t>
+          <t>201 {}; {"result":"SUCCESS","errorMessage":null}</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
+          <t>Нужны примеры ответов, которые можно считать ожидаемыми.
+Например: getProcessParams=SUCCESS; HTTP 200/201; result=SUCCESS.
+Источник: *WorkerIT + stubs/ump/ump_application_response_200.json.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1182,6 +1242,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>HTTP create-contract: 201 Created, body {{}}
+          <t>HTTP create-contract: 201 Created, body {}
 Camunda worker out success:
 { "result": "SUCCESS", "errorMessage": null }
 HTTP 503 → 3 retry →:
@@ -1242,14 +1242,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-finalisation-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -565,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -632,7 +639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -904,7 +911,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of) · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -1257,11 +1264,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1274,14 +1281,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>Полные request/response (не только имя метода). Источник: develop ump-ncins-pa@4a921a1653e + *WorkerIT + stubs. · полные HTTP body</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Методы finalisation (develop + IT)</t>
+          <t>HTTP / JobWorker — полные тела запросов и ответов</t>
         </is>
       </c>
     </row>
@@ -1293,123 +1300,352 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN / JobWorker</t>
+          <t>Метод / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Где</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / HTTP</t>
+          <t>Полный REQUEST (headers + body)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Request / Input</t>
+          <t>Полный RESPONSE (status + body)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Response / Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationDataWorker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>GET /applications/{id}</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>processType=FINALISATION</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>поля договора + agreement/policy/contractLink</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>ump-finalisation-ncins-pa.create-contract</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>FinalisationWorker</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>POST /v1/ins-contracts</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>ContractRequestDto + headers A-*</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>201 {}; worker result=SUCCESS|ERROR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>ea-send ×3</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>внешний connector</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>ump-document-connectors.ea-send-documents.v1</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>acId=agreement|policy|contractLink; stopInIncident=false</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>вне репы</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>get-application-data
+GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker
+все процессы</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET /applications/6dc5daf3-da12-4aae-9766-572da7b6b003?include=PARTICIPANT&amp;include=PRODUCT HTTP/1.1
+Host: ump-application-facade.ump.svc.cluster.local
+Accept: application/json
+(без body)
+Camunda job input:
+{
+  "businessKey": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "processType": "&lt;PREPARE_DOCUMENTS|SIGNING|PAYMENT|FINALISATION|DELETE_DOCS&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+{
+  "externalApplicationIds": [
+    {
+      "extAppId": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+      "systemCode": "SFA",
+      "extAppCreateDate": "2026-06-25T12:45:34.785179Z"
+    }
+  ],
+  "channels": [
+    {
+      "id": "bd458000-77c2-48af-91b4-815f7ef2d4e6",
+      "userInfo": {
+        "userId": "f6753df0-b5c9-4828-a7b7-f9f3f7d8f33c",
+        "login": "service-account-nib-corp-ncins"
+      },
+      "code": "nib-corp-ncins",
+      "name": "НИБ. Страхование",
+      "isDeleted": false,
+      "category": "RECEIVE",
+      "type": "BANK_SYSTEM"
+    }
+  ],
+  "participants": [
+    {
+      "id": "bdec62a5-e10a-4c5b-86c7-b5ac190b8055",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "isDeleted": false,
+      "contacts": [
+        {
+          "type": "EMAIL",
+          "typeName": "Email",
+          "value": "romashka@rambler.ru",
+          "isPrimary": false
+        },
+        {
+          "type": "PHONE",
+          "typeName": "Телефон",
+          "value": "79183221488",
+          "isPrimary": false
+        }
+      ],
+      "addresses": [
+        {
+          "type": "FACT",
+          "typeName": "Адрес проживания / фактический - краткий",
+          "address": {
+            "fullAddress": "Г. Пушкино ул. Колотушкина д. 14/88"
+          }
+        }
+      ],
+      "identityDocuments": [],
+      "okveds": [],
+      "licenses": [],
+      "management": [],
+      "founders": [],
+      "externalPins": [],
+      "pin": "AAAXYX",
+      "type": "LEGAL",
+      "typeName": "Юридическое лицо",
+      "fullName": "ООО Звезда",
+      "inn": "7826688577",
+      "createDate": "2026-07-09T17:19:18.963685Z",
+      "lastUpdateDate": "2026-07-09T17:19:19.99786Z",
+      "citizenship": "Россия",
+      "citizenshipCode": "RU",
+      "taxCountryCode": "RU",
+      "ogrn": "1027810281740"
+    }
+  ],
+  "products": [
+    {
+      "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "status": {
+        "isTerminate": true,
+        "code": "COMPLETE",
+        "name": "Завершен"
+      },
+      "stage": {
+        "code": "PAYMENT_COMPLETED",
+        "name": "PAYMENT_COMPLETED"
+      },
+      "createDate": "2026-07-09T17:19:18.891861Z",
+      "lastUpdateDate": "2026-07-09T17:23:50.600316Z",
+      "code": "NON_CREDIT_INSURANCE",
+      "name": "Некредитное страхование ЮЛ",
+      "type": "PRODUCT",
+      "main": false,
+      "isDeleted": false,
+      "responsibleManager": {
+        "login": "U_M13RU"
+      },
+      "salesChannel": {
+        "code": "SFA",
+        "name": "SFA"
+      },
+      "productProperties": {
+        "programId": 1073741824,
+        "beginDate": "2026-06-25T11:47:13.57Z",
+        "endDate": "2026-06-25T11:47:13.57Z",
+        "signDate": "2026-06-25T11:47:13.57Z",
+        "duration": 12,
+        "insuranceSum": 20000.0,
+        "insurancePremium": 20000.0,
+        "contractNumber": "1423423/sdf/123",
+        "paymentType": "payment_account",
+        "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+        "insuranceObjects": [
+          {
+            "paymentAccount": "123523464567347"
+          }
+        ],
+        "code": "NON_CREDIT_INSURANCE"
+      },
+      "channelCode": "nib-corp-ncins"
+    }
+  ],
+  "options": [],
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "createDate": "2026-07-09T17:19:18.833504Z",
+  "lastUpdateDate": "2026-07-09T17:22:46.462517Z",
+  "number": "UMP26070994592",
+  "statusCode": "COMPLETE",
+  "statusName": "Завершена",
+  "finalVersion": true,
+  "isDeleted": false
+}
+Camunda job output (успех):
+{ "getProcessParams": "SUCCESS", ...поля по processType из ApplicationMapper }
+Ошибка:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT
+stubs/ump/ump_application_response_200.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="420" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ump-finalisation-ncins-pa.create-contract
+POST /v1/ins-contracts</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>FinalisationWorker
+finalisation</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>POST /v1/ins-contracts HTTP/1.1
+Host: corp-gateway-test.moscow.alfaintra.net
+  /corp-ncins-acc-gateway/secure/corp-ncins-acc-corp-ncins-acc-api
+Content-Type: application/json
+A-userId: AAAX22
+A-customerId: AAAX22
+A-clientType: BACKEND
+A-channelId: ump
+A-projectId: ncins
+Authorization: Bearer &lt;keycloak access_token&gt;
+{
+  "programId": 3,
+  "contractNumber": "Z6922/888/ABR14880/10",
+  "beginDate": "2027-07-01T00:00:00Z",
+  "endDate": "2028-07-01T00:00:00Z",
+  "signDate": "2027-07-01T00:00:00Z",
+  "insuranceSum": 150000.93,
+  "insurancePremium": 50000.55,
+  "debitAccount": "40802810000000000000",
+  "duration": 12,
+  "paymentType": "payment_account",
+  "contractLink": "http://contract.link",
+  "policyLink": "http://policy.link",
+  "agreementLink": "http://agreement.link",
+  "sellerId": "ASASAS",
+  "sellerChannel": "SFA",
+  "owner": {
+    "inn": "7707083893",
+    "email": "romashka@rambler.ru",
+    "ownerId": "AAAX22",
+    "ogrn": null,
+    "phoneNumber": "+79001234567",
+    "legalAddress": "г. Пушкино ул. Колотушкина д. 14/88"
+  },
+  "insuranceObjects": [
+    {
+      "employeeFIO": "Иванов Иван Иванович",
+      "employeeEmail": "ivanov.ii@example.com",
+      "employeePhoneNumber": "+7 (999) 123-45-67",
+      "employeeBirthDate": "1985-05-15",
+      "paymentAccount": "40817810099910004312",
+      "cadastralNumber": "77:01:0001045:32",
+      "area": 45.5,
+      "realEstateAddress": "г. Москва, ул. Тверская, д. 15, кв. 78",
+      "realEstateType": "COMMERCIAL"
+    },
+    {
+      "employeeFIO": "Иванов Иван Иванович",
+      "employeeEmail": "ivanov.ii@example.com",
+      "employeePhoneNumber": "+7 (999) 123-45-67",
+      "employeeBirthDate": "1985-05-15",
+      "paymentAccount": "40817810099910004312",
+      "cadastralNumber": "77:01:0001045:32",
+      "area": 45.5,
+      "realEstateAddress": "г. Москва, ул. Тверская, д. 15, кв. 78",
+      "realEstateType": "RESIDENTIAL"
+    }
+  ]
+}
+Источник: FinalisationWorkerIT.createValidVariables + ContractMapper → ContractRequestDto.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 201 Created
+Content-Type: application/json
+{}
+Camunda job output:
+{
+  "result": "SUCCESS",
+  "errorMessage": null
+}
+HTTP 503 (после 3 retry):
+{
+  "result": "ERROR",
+  "errorMessage": "&lt;exception log&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>FinalisationWorkerIT
+ContractMapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ump-document-connectors.ea-send-documents.v1
+×3 parallel</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>внешний connector
+finalisation</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Connector (вне ump-ncins-pa): ump-document-connectors.ea-send-documents.v1
+×3 параллельно после create-contract
+Input (BPMN):
+{
+  "acId": "&lt;agreementLink | policyLink | contractLink&gt;",
+  "stopInIncident": false
+}
+Полный HTTP body connector — в репе ncins нет (внешний модуль).</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Response необязателен.
+stopInIncident=false — отсутствие документов не обязано ронять в инцидент.
+Полный response TBD (модуль document-connectors).</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>BPMN finalisation
+(код connector вне репы)</t>
         </is>
       </c>
     </row>
